--- a/marketer_forms/011_e_commerce_survey--marketer_forms.xlsx
+++ b/marketer_forms/011_e_commerce_survey--marketer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_1_time_a_month'}</t>
+          <t>less_than_1_time_a_month</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than 1 time a month'}</t>
+          <t>Less than 1 time a month</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'1_time_a_month'}</t>
+          <t>1_time_a_month</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '1 time a month'}</t>
+          <t>1 time a month</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'2_times_a_month'}</t>
+          <t>2_times_a_month</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '2 times a month'}</t>
+          <t>2 times a month</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'more_than_2_times_a_month'}</t>
+          <t>more_than_2_times_a_month</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'More than 2 times a month'}</t>
+          <t>More than 2 times a month</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'more_than_5_times_a_month'}</t>
+          <t>more_than_5_times_a_month</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'More than 5 times a month'}</t>
+          <t>More than 5 times a month</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_$25k'}</t>
+          <t>less_than_$25k</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than $25k'}</t>
+          <t>Less than $25k</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'$25-49k'}</t>
+          <t>$25-49k</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '$25-49k'}</t>
+          <t>$25-49k</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'$50-74k'}</t>
+          <t>$50-74k</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '$50-74k'}</t>
+          <t>$50-74k</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'$75-99k'}</t>
+          <t>$75-99k</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '$75-99k'}</t>
+          <t>$75-99k</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'more_than_$100k'}</t>
+          <t>more_than_$100k</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'More than $100k'}</t>
+          <t>More than $100k</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_10'}</t>
+          <t>less_than_10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than 10'}</t>
+          <t>Less than 10</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'10-49'}</t>
+          <t>10-49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '10-49'}</t>
+          <t>10-49</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'50-99'}</t>
+          <t>50-99</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '50-99'}</t>
+          <t>50-99</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'100-499'}</t>
+          <t>100-499</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '100-499'}</t>
+          <t>100-499</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'500_or_more'}</t>
+          <t>500_or_more</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '500 or more'}</t>
+          <t>500 or more</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_high_school'}</t>
+          <t>less_than_high_school</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than High School'}</t>
+          <t>Less than High School</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'high_school_graduation'}</t>
+          <t>high_school_graduation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'High School Graduation'}</t>
+          <t>High School Graduation</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bachelors'}</t>
+          <t>bachelors</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bachelors'}</t>
+          <t>Bachelors</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'masters'}</t>
+          <t>masters</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Masters'}</t>
+          <t>Masters</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'doctoral_or_higher'}</t>
+          <t>doctoral_or_higher</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Doctoral or higher'}</t>
+          <t>Doctoral or higher</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'amazon'}</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Amazon'}</t>
+          <t>Amazon</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'ebay'}</t>
+          <t>ebay</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'eBay'}</t>
+          <t>eBay</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'etsy'}</t>
+          <t>etsy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Etsy'}</t>
+          <t>Etsy</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'electronics'}</t>
+          <t>electronics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Electronics'}</t>
+          <t>Electronics</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fashion'}</t>
+          <t>fashion</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fashion'}</t>
+          <t>Fashion</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'home_&amp;_garden'}</t>
+          <t>home_&amp;_garden</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Home &amp; Garden'}</t>
+          <t>Home &amp; Garden</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'beauty_&amp;_personal_care'}</t>
+          <t>beauty_&amp;_personal_care</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Beauty &amp; Personal Care'}</t>
+          <t>Beauty &amp; Personal Care</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'desktop'}</t>
+          <t>desktop</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Desktop'}</t>
+          <t>Desktop</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'laptop'}</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Laptop'}</t>
+          <t>Laptop</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'smartphone'}</t>
+          <t>smartphone</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Smartphone'}</t>
+          <t>Smartphone</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'tablet'}</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Tablet'}</t>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'google_chrome'}</t>
+          <t>google_chrome</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Google Chrome'}</t>
+          <t>Google Chrome</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mozilla_firefox'}</t>
+          <t>mozilla_firefox</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mozilla Firefox'}</t>
+          <t>Mozilla Firefox</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'safari'}</t>
+          <t>safari</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Safari'}</t>
+          <t>Safari</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'opera'}</t>
+          <t>opera</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Opera'}</t>
+          <t>Opera</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'google'}</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Google'}</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'bing'}</t>
+          <t>bing</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Bing'}</t>
+          <t>Bing</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'yahoo'}</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Yahoo'}</t>
+          <t>Yahoo</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'windows'}</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Windows'}</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'macos'}</t>
+          <t>macos</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'macOS'}</t>
+          <t>macOS</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'linux'}</t>
+          <t>linux</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Linux'}</t>
+          <t>Linux</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'desktop'}</t>
+          <t>desktop</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Desktop'}</t>
+          <t>Desktop</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'laptop'}</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Laptop'}</t>
+          <t>Laptop</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Mobile'}</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Mobile'}</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'mobile_phone'}</t>
+          <t>mobile_phone</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Mobile Phone'}</t>
+          <t>Mobile Phone</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'laptops'}</t>
+          <t>laptops</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Laptops'}</t>
+          <t>Laptops</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'tablets'}</t>
+          <t>tablets</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Tablets'}</t>
+          <t>Tablets</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'desktop'}</t>
+          <t>desktop</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Desktop'}</t>
+          <t>Desktop</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'windows'}</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Windows'}</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'macos'}</t>
+          <t>macos</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'macOS'}</t>
+          <t>macOS</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'chrome'}</t>
+          <t>chrome</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Chrome'}</t>
+          <t>Chrome</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'safari'}</t>
+          <t>safari</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Safari'}</t>
+          <t>Safari</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'firefox'}</t>
+          <t>firefox</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Firefox'}</t>
+          <t>Firefox</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
